--- a/SFY_ADA_4G_BOM.xlsx
+++ b/SFY_ADA_4G_BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\romain.saint-paul\Desktop\PERSO\elec\SOMFY_ADA\GSM_4G\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{160BF342-9B62-4369-8C80-3553BFFF4909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D48637-F397-45A9-A232-2607D5107A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B9147F25-2B7F-49AE-B50F-26EF9D48D8E0}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{B9147F25-2B7F-49AE-B50F-26EF9D48D8E0}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_GSM_4G" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="149">
   <si>
     <t>Name</t>
   </si>
@@ -212,15 +212,9 @@
     <t>0R</t>
   </si>
   <si>
-    <t>R2, R27, R31, R58, R59</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
-    <t>R1, R14, R17, R23, R24, R25, R29, R32, R39, R44, R48, R54, R56, R57, R60</t>
-  </si>
-  <si>
     <t>SI2300</t>
   </si>
   <si>
@@ -459,6 +453,42 @@
   </si>
   <si>
     <t>PAD</t>
+  </si>
+  <si>
+    <t>R1, R14, R17, R23, R24, R25, R29, R32, R39, R44, R48, R54, R58, R59, R60</t>
+  </si>
+  <si>
+    <t>R2, R27, R31, R56, R57</t>
+  </si>
+  <si>
+    <t>Equivalence</t>
+  </si>
+  <si>
+    <t>2452796-1 TE-connectivity</t>
+  </si>
+  <si>
+    <t>693042010611 Wurth</t>
+  </si>
+  <si>
+    <t>MCP73833-AMI</t>
+  </si>
+  <si>
+    <t>LM1117MP-3.3/NOPB TEXAS INSTRUMENTS / LM1117MPX-33NOPB onsemi</t>
+  </si>
+  <si>
+    <t>61300311121 Wurth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BF100-14-A-C-0-0625-L-C GCT /  MMS-107-02-F-DV-K-TR Samtec </t>
+  </si>
+  <si>
+    <t>621014242921 Wurth</t>
+  </si>
+  <si>
+    <t>65100516121 Wurth</t>
+  </si>
+  <si>
+    <t>60311042114502 Wurth</t>
   </si>
 </sst>
 </file>
@@ -901,17 +931,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3581317-A5B4-4DED-AAE4-5FD40177DD49}">
-  <dimension ref="A1:F49"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G49"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="70.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="70.15234375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="20" customWidth="1"/>
+    <col min="4" max="4" width="28.69140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -928,180 +958,192 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
-      <c r="F2" s="7"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F2" s="6"/>
+      <c r="G2" s="7"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="E3" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A6" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A8" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A9" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F3" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F4" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F5" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F6" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F7" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F8" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F9" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" s="5" t="s">
         <v>32</v>
       </c>
@@ -1109,14 +1151,15 @@
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
-      <c r="F11" s="7"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F11" s="6"/>
+      <c r="G11" s="7"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>30</v>
@@ -1127,16 +1170,17 @@
       <c r="E12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F12" s="2"/>
+      <c r="G12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>34</v>
@@ -1147,16 +1191,17 @@
       <c r="E13" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F13" s="2"/>
+      <c r="G13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>36</v>
@@ -1167,16 +1212,17 @@
       <c r="E14" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F14" s="2"/>
+      <c r="G14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>38</v>
@@ -1187,16 +1233,17 @@
       <c r="E15" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F15" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F15" s="2"/>
+      <c r="G15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>40</v>
@@ -1207,16 +1254,17 @@
       <c r="E16" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="2"/>
+      <c r="G16" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>42</v>
@@ -1227,16 +1275,17 @@
       <c r="E17" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17" s="2"/>
+      <c r="G17" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>44</v>
@@ -1247,16 +1296,17 @@
       <c r="E18" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F18" s="2"/>
+      <c r="G18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>46</v>
@@ -1267,16 +1317,17 @@
       <c r="E19" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19" s="2"/>
+      <c r="G19" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A20" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>48</v>
@@ -1287,16 +1338,17 @@
       <c r="E20" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F20" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F20" s="2"/>
+      <c r="G20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A21" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>50</v>
@@ -1307,16 +1359,17 @@
       <c r="E21" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21" s="2"/>
+      <c r="G21" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>52</v>
@@ -1327,16 +1380,17 @@
       <c r="E22" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F22" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F22" s="2"/>
+      <c r="G22" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A23" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>54</v>
@@ -1347,19 +1401,20 @@
       <c r="E23" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23" s="2"/>
+      <c r="G23" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A24" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>31</v>
@@ -1367,19 +1422,20 @@
       <c r="E24" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24" s="2"/>
+      <c r="G24" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>58</v>
+        <v>137</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>31</v>
@@ -1387,131 +1443,139 @@
       <c r="E25" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25" s="2"/>
+      <c r="G25" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A26" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
-      <c r="F26" s="7"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F26" s="6"/>
+      <c r="G26" s="7"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A27" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="F27" s="2"/>
+      <c r="G27" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="B28" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="F27" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+      <c r="D28" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F28" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F28" s="2"/>
+      <c r="G28" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A29" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="E29" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="F29" s="2"/>
+      <c r="G29" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="B30" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="F29" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
+      <c r="C30" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="F30" s="2"/>
+      <c r="G30" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="B31" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F30" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
+      <c r="C31" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="D31" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="E31" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F31" s="1">
+      <c r="F31" s="2"/>
+      <c r="G31" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A32" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
-      <c r="F32" s="7"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F32" s="6"/>
+      <c r="G32" s="7"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A33" s="2" t="s">
         <v>6</v>
       </c>
@@ -1527,11 +1591,12 @@
       <c r="E33" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F33" s="2"/>
+      <c r="G33" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A34" s="2" t="s">
         <v>10</v>
       </c>
@@ -1547,11 +1612,12 @@
       <c r="E34" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F34" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F34" s="2"/>
+      <c r="G34" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A35" s="2" t="s">
         <v>14</v>
       </c>
@@ -1567,13 +1633,14 @@
       <c r="E35" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F35" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F35" s="2"/>
+      <c r="G35" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>11</v>
@@ -1585,13 +1652,14 @@
         <v>17</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F36" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+      <c r="F36" s="2"/>
+      <c r="G36" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
         <v>19</v>
       </c>
@@ -1605,13 +1673,14 @@
         <v>21</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F37" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="F37" s="2"/>
+      <c r="G37" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" s="2" t="s">
         <v>22</v>
       </c>
@@ -1627,11 +1696,14 @@
       <c r="E38" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F38" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F38" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G38" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
         <v>28</v>
       </c>
@@ -1647,198 +1719,212 @@
       <c r="E39" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F39" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F39" s="2"/>
+      <c r="G39" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
-      <c r="F40" s="7"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F40" s="6"/>
+      <c r="G40" s="7"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="D41" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G41" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A42" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="B42" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D41" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F41" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
+      <c r="C42" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="D42" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F42" s="2"/>
+      <c r="G42" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A43" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="B43" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D42" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F42" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
+      <c r="C43" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="D43" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F43" s="2"/>
+      <c r="G43" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A44" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="B44" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D43" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F43" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
+      <c r="C44" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="D44" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G44" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A45" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="B45" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D44" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F44" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
+      <c r="C45" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="D45" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="E45" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F45" s="2"/>
+      <c r="G45" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A46" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="B46" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F45" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
+      <c r="C46" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="D46" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F46" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G46" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A47" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
-      <c r="F47" s="7"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F47" s="6"/>
+      <c r="G47" s="7"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A48" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="D48" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="E48" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="F48" s="2"/>
+      <c r="G48" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A49" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="B49" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F48" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
+      <c r="D49" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C49" s="2" t="s">
+      <c r="E49" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D49" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F49" s="1">
+      <c r="F49" s="2"/>
+      <c r="G49" s="1">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A32:G32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
